--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/129.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/129.xlsx
@@ -426,13 +426,13 @@
         <v>-16.76193184682177</v>
       </c>
       <c r="E2">
-        <v>-8.057900798846122</v>
+        <v>-12.62741183797399</v>
       </c>
       <c r="F2">
-        <v>-4.827537331362591</v>
+        <v>-5.634206478413167</v>
       </c>
       <c r="G2">
-        <v>-7.4049598914538</v>
+        <v>-9.113274221719596</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-16.74361025443589</v>
       </c>
       <c r="E3">
-        <v>-8.410388158655167</v>
+        <v>-12.7518724176008</v>
       </c>
       <c r="F3">
-        <v>-4.432037456732981</v>
+        <v>-6.116766938709602</v>
       </c>
       <c r="G3">
-        <v>-7.419602434373997</v>
+        <v>-8.869108246016189</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-16.57603110447161</v>
       </c>
       <c r="E4">
-        <v>-9.558184237587311</v>
+        <v>-13.33388095401461</v>
       </c>
       <c r="F4">
-        <v>-4.817103215556928</v>
+        <v>-5.848209398354599</v>
       </c>
       <c r="G4">
-        <v>-6.800169569066504</v>
+        <v>-8.811259773262965</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-16.24901507583272</v>
       </c>
       <c r="E5">
-        <v>-10.63506441355934</v>
+        <v>-14.24499181046185</v>
       </c>
       <c r="F5">
-        <v>-4.483039209355944</v>
+        <v>-5.590275669940501</v>
       </c>
       <c r="G5">
-        <v>-7.0386612697156</v>
+        <v>-8.643769342794618</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-15.78364468343329</v>
       </c>
       <c r="E6">
-        <v>-10.68238243846548</v>
+        <v>-14.25241397936043</v>
       </c>
       <c r="F6">
-        <v>-4.918793597924596</v>
+        <v>-5.575993787548834</v>
       </c>
       <c r="G6">
-        <v>-6.45869341778176</v>
+        <v>-8.308662681127432</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-15.19449387255383</v>
       </c>
       <c r="E7">
-        <v>-10.98921825180321</v>
+        <v>-15.46588198835181</v>
       </c>
       <c r="F7">
-        <v>-4.90766613860279</v>
+        <v>-5.540581081079155</v>
       </c>
       <c r="G7">
-        <v>-6.922851765660816</v>
+        <v>-8.413001144888641</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-14.49692866624432</v>
       </c>
       <c r="E8">
-        <v>-10.68191147716869</v>
+        <v>-16.84693523494504</v>
       </c>
       <c r="F8">
-        <v>-4.335048059376201</v>
+        <v>-5.658326880447882</v>
       </c>
       <c r="G8">
-        <v>-6.399236019896449</v>
+        <v>-7.945088638368052</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-13.70882626691433</v>
       </c>
       <c r="E9">
-        <v>-12.46933639578824</v>
+        <v>-17.01105618993103</v>
       </c>
       <c r="F9">
-        <v>-4.735870194568798</v>
+        <v>-5.385161960598509</v>
       </c>
       <c r="G9">
-        <v>-6.088018254840644</v>
+        <v>-7.80251006308272</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-12.84001651290426</v>
       </c>
       <c r="E10">
-        <v>-14.05777110956274</v>
+        <v>-18.1218501077465</v>
       </c>
       <c r="F10">
-        <v>-4.349571825049485</v>
+        <v>-5.638149507250492</v>
       </c>
       <c r="G10">
-        <v>-5.509536837853935</v>
+        <v>-7.946164565668314</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-11.9111582374929</v>
       </c>
       <c r="E11">
-        <v>-15.22018057411763</v>
+        <v>-18.59516621102821</v>
       </c>
       <c r="F11">
-        <v>-4.444238480208815</v>
+        <v>-5.220277914173476</v>
       </c>
       <c r="G11">
-        <v>-5.425167584785609</v>
+        <v>-7.193826539141241</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-10.94882866616355</v>
       </c>
       <c r="E12">
-        <v>-16.60576682319255</v>
+        <v>-19.05387798563518</v>
       </c>
       <c r="F12">
-        <v>-4.53089068074606</v>
+        <v>-5.216287668394191</v>
       </c>
       <c r="G12">
-        <v>-4.87939766827244</v>
+        <v>-7.152385130080645</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-9.978165018703415</v>
       </c>
       <c r="E13">
-        <v>-15.69360083230152</v>
+        <v>-20.45156884573259</v>
       </c>
       <c r="F13">
-        <v>-4.726763951709823</v>
+        <v>-5.55512886940712</v>
       </c>
       <c r="G13">
-        <v>-4.021118873943149</v>
+        <v>-6.562326735343105</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-9.04529570153643</v>
       </c>
       <c r="E14">
-        <v>-17.21986412642471</v>
+        <v>-20.57470258247516</v>
       </c>
       <c r="F14">
-        <v>-4.57246726905997</v>
+        <v>-5.269021537256407</v>
       </c>
       <c r="G14">
-        <v>-5.081509783990485</v>
+        <v>-6.12192155170832</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-8.19201590291298</v>
       </c>
       <c r="E15">
-        <v>-18.8031544937265</v>
+        <v>-22.0315670124308</v>
       </c>
       <c r="F15">
-        <v>-4.158112095607838</v>
+        <v>-5.052815988390931</v>
       </c>
       <c r="G15">
-        <v>-3.037787532413429</v>
+        <v>-5.663040213418862</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-7.457865867850399</v>
       </c>
       <c r="E16">
-        <v>-18.39262568256114</v>
+        <v>-22.60504843228817</v>
       </c>
       <c r="F16">
-        <v>-3.924422195971472</v>
+        <v>-5.085022913011775</v>
       </c>
       <c r="G16">
-        <v>-3.678689285543095</v>
+        <v>-5.510616075699738</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-6.878772087723552</v>
       </c>
       <c r="E17">
-        <v>-19.67471818666476</v>
+        <v>-23.22109750781764</v>
       </c>
       <c r="F17">
-        <v>-4.086118684630533</v>
+        <v>-4.686308972859304</v>
       </c>
       <c r="G17">
-        <v>-2.632179492941923</v>
+        <v>-5.17542665039407</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-6.46830067891599</v>
       </c>
       <c r="E18">
-        <v>-19.9396475015355</v>
+        <v>-24.14124266991018</v>
       </c>
       <c r="F18">
-        <v>-3.986539810772601</v>
+        <v>-4.493239725554017</v>
       </c>
       <c r="G18">
-        <v>-3.221661852755629</v>
+        <v>-5.602371155866178</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-6.229886919673349</v>
       </c>
       <c r="E19">
-        <v>-21.010907841264</v>
+        <v>-24.3993702168214</v>
       </c>
       <c r="F19">
-        <v>-3.660142344884526</v>
+        <v>-4.477520625718493</v>
       </c>
       <c r="G19">
-        <v>-4.23306330991283</v>
+        <v>-5.515754042376687</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-6.15757548350563</v>
       </c>
       <c r="E20">
-        <v>-20.30139106221622</v>
+        <v>-25.90035556903378</v>
       </c>
       <c r="F20">
-        <v>-3.125044338800338</v>
+        <v>-3.925801427697133</v>
       </c>
       <c r="G20">
-        <v>-2.869886594298212</v>
+        <v>-6.250367408086503</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-6.236658221194044</v>
       </c>
       <c r="E21">
-        <v>-21.48715839570268</v>
+        <v>-26.02409612129338</v>
       </c>
       <c r="F21">
-        <v>-2.777620423127003</v>
+        <v>-3.670805090093361</v>
       </c>
       <c r="G21">
-        <v>-3.316919490102618</v>
+        <v>-6.218318016720819</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-6.453530863725272</v>
       </c>
       <c r="E22">
-        <v>-22.87637648093175</v>
+        <v>-26.95222951153545</v>
       </c>
       <c r="F22">
-        <v>-2.062836273497157</v>
+        <v>-3.376454673917391</v>
       </c>
       <c r="G22">
-        <v>-3.508050526266901</v>
+        <v>-6.731479059672166</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-6.783159062819879</v>
       </c>
       <c r="E23">
-        <v>-22.79840521546768</v>
+        <v>-26.52935155175118</v>
       </c>
       <c r="F23">
-        <v>-2.112321285405594</v>
+        <v>-3.013744894560196</v>
       </c>
       <c r="G23">
-        <v>-3.403030090124601</v>
+        <v>-6.060769154506903</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-7.198486532310323</v>
       </c>
       <c r="E24">
-        <v>-23.4628953774572</v>
+        <v>-27.5945392078354</v>
       </c>
       <c r="F24">
-        <v>-1.903874225634737</v>
+        <v>-3.238081697851553</v>
       </c>
       <c r="G24">
-        <v>-5.30288596420155</v>
+        <v>-6.801093211271961</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-7.668961309193151</v>
       </c>
       <c r="E25">
-        <v>-22.86956565602421</v>
+        <v>-26.80523524524647</v>
       </c>
       <c r="F25">
-        <v>-2.116073789740275</v>
+        <v>-3.035679235018924</v>
       </c>
       <c r="G25">
-        <v>-4.995280004329088</v>
+        <v>-7.188873963014491</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-8.154621765745308</v>
       </c>
       <c r="E26">
-        <v>-23.38764119639773</v>
+        <v>-27.4723292797904</v>
       </c>
       <c r="F26">
-        <v>-1.931726422819065</v>
+        <v>-2.875260088894981</v>
       </c>
       <c r="G26">
-        <v>-4.905584083488075</v>
+        <v>-7.310927155956342</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-8.618223442972546</v>
       </c>
       <c r="E27">
-        <v>-23.26453915897322</v>
+        <v>-27.06012946171622</v>
       </c>
       <c r="F27">
-        <v>-2.065452257755198</v>
+        <v>-2.572739485025198</v>
       </c>
       <c r="G27">
-        <v>-5.090908422776477</v>
+        <v>-7.240932291619531</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-9.023700196104121</v>
       </c>
       <c r="E28">
-        <v>-23.3333085652537</v>
+        <v>-26.77611715737715</v>
       </c>
       <c r="F28">
-        <v>-1.48082699302503</v>
+        <v>-2.496923158483974</v>
       </c>
       <c r="G28">
-        <v>-5.086839762308712</v>
+        <v>-7.697923308406065</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-9.342000033733456</v>
       </c>
       <c r="E29">
-        <v>-23.37784157864513</v>
+        <v>-26.97538359913667</v>
       </c>
       <c r="F29">
-        <v>-1.642464667598492</v>
+        <v>-2.766746444230454</v>
       </c>
       <c r="G29">
-        <v>-5.647447543928894</v>
+        <v>-7.958741328172006</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-9.556603106200788</v>
       </c>
       <c r="E30">
-        <v>-22.99771694196728</v>
+        <v>-26.14699437738754</v>
       </c>
       <c r="F30">
-        <v>-1.351840248000313</v>
+        <v>-2.555366963853687</v>
       </c>
       <c r="G30">
-        <v>-5.228229851745446</v>
+        <v>-7.721116990454199</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-9.660157009284379</v>
       </c>
       <c r="E31">
-        <v>-21.77706224472572</v>
+        <v>-26.43784467747819</v>
       </c>
       <c r="F31">
-        <v>-1.711638315936667</v>
+        <v>-2.401136550596058</v>
       </c>
       <c r="G31">
-        <v>-5.782537665204395</v>
+        <v>-8.082840438257126</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-9.661612392097727</v>
       </c>
       <c r="E32">
-        <v>-22.30679860566899</v>
+        <v>-26.13786497378808</v>
       </c>
       <c r="F32">
-        <v>-1.245761175132614</v>
+        <v>-2.16838684796187</v>
       </c>
       <c r="G32">
-        <v>-5.151345742141411</v>
+        <v>-7.724891012368968</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-9.58284946074955</v>
       </c>
       <c r="E33">
-        <v>-22.01187267897145</v>
+        <v>-25.81503006178126</v>
       </c>
       <c r="F33">
-        <v>-1.62787049069597</v>
+        <v>-2.44842141868266</v>
       </c>
       <c r="G33">
-        <v>-5.002573136152103</v>
+        <v>-7.369229173448447</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-9.449567355624295</v>
       </c>
       <c r="E34">
-        <v>-22.44143466639104</v>
+        <v>-25.52640324242838</v>
       </c>
       <c r="F34">
-        <v>-1.604165929097459</v>
+        <v>-2.376136422379569</v>
       </c>
       <c r="G34">
-        <v>-5.761562048667573</v>
+        <v>-7.487660629570334</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-9.295814842297416</v>
       </c>
       <c r="E35">
-        <v>-21.3272353361218</v>
+        <v>-24.85224478843249</v>
       </c>
       <c r="F35">
-        <v>-1.120845027525254</v>
+        <v>-2.150258855719005</v>
       </c>
       <c r="G35">
-        <v>-5.764667340383409</v>
+        <v>-7.764554658474976</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-9.152809830372455</v>
       </c>
       <c r="E36">
-        <v>-20.63856765140533</v>
+        <v>-24.66526862512978</v>
       </c>
       <c r="F36">
-        <v>-1.199957427962218</v>
+        <v>-2.281269302308762</v>
       </c>
       <c r="G36">
-        <v>-4.042008416295951</v>
+        <v>-7.531154576865279</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-9.043508195947602</v>
       </c>
       <c r="E37">
-        <v>-20.99701901148248</v>
+        <v>-24.58680375599888</v>
       </c>
       <c r="F37">
-        <v>-1.200962237621814</v>
+        <v>-2.357709389504294</v>
       </c>
       <c r="G37">
-        <v>-5.276093719152228</v>
+        <v>-7.204741407784218</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-8.98406849430609</v>
       </c>
       <c r="E38">
-        <v>-19.13391423524674</v>
+        <v>-23.8916377110814</v>
       </c>
       <c r="F38">
-        <v>-1.068517887057812</v>
+        <v>-2.147589855947186</v>
       </c>
       <c r="G38">
-        <v>-4.272882551659184</v>
+        <v>-7.312224889807736</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-8.979095252547268</v>
       </c>
       <c r="E39">
-        <v>-19.06664828233681</v>
+        <v>-23.49522868187196</v>
       </c>
       <c r="F39">
-        <v>-1.148505871839536</v>
+        <v>-2.349648546307652</v>
       </c>
       <c r="G39">
-        <v>-4.9130129476782</v>
+        <v>-6.807859966354231</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-9.022993816467645</v>
       </c>
       <c r="E40">
-        <v>-17.70850911422238</v>
+        <v>-23.57535097248967</v>
       </c>
       <c r="F40">
-        <v>-1.119652178465223</v>
+        <v>-2.149253217692007</v>
       </c>
       <c r="G40">
-        <v>-4.131565294224314</v>
+        <v>-6.993800067112937</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-9.104978731276228</v>
       </c>
       <c r="E41">
-        <v>-18.1941109674869</v>
+        <v>-22.57709869071283</v>
       </c>
       <c r="F41">
-        <v>-1.087293662609666</v>
+        <v>-2.3315835099874</v>
       </c>
       <c r="G41">
-        <v>-3.967501278389113</v>
+        <v>-6.65814716543177</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-9.206172790673538</v>
       </c>
       <c r="E42">
-        <v>-17.91257120995602</v>
+        <v>-21.54506852131277</v>
       </c>
       <c r="F42">
-        <v>-1.296371938341456</v>
+        <v>-2.626600761922625</v>
       </c>
       <c r="G42">
-        <v>-4.346499152815957</v>
+        <v>-6.734928648124087</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-9.307836716276693</v>
       </c>
       <c r="E43">
-        <v>-17.81122849013837</v>
+        <v>-21.96948163378564</v>
       </c>
       <c r="F43">
-        <v>-1.464747553369289</v>
+        <v>-2.617245180475408</v>
       </c>
       <c r="G43">
-        <v>-4.106537569947425</v>
+        <v>-6.087475325372203</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-9.39781890389704</v>
       </c>
       <c r="E44">
-        <v>-17.58700109964857</v>
+        <v>-21.59204691066834</v>
       </c>
       <c r="F44">
-        <v>-1.249536873754574</v>
+        <v>-2.539133447861025</v>
       </c>
       <c r="G44">
-        <v>-4.579958824245361</v>
+        <v>-6.13396200583465</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-9.462799538523129</v>
       </c>
       <c r="E45">
-        <v>-16.59778765199103</v>
+        <v>-20.06969621808777</v>
       </c>
       <c r="F45">
-        <v>-1.537332418672193</v>
+        <v>-2.647747324981291</v>
       </c>
       <c r="G45">
-        <v>-4.387083130581883</v>
+        <v>-6.695099474741116</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-9.498938767388026</v>
       </c>
       <c r="E46">
-        <v>-17.27496659815004</v>
+        <v>-20.77535020880702</v>
       </c>
       <c r="F46">
-        <v>-1.703791191529948</v>
+        <v>-2.830467778323403</v>
       </c>
       <c r="G46">
-        <v>-3.446024145043116</v>
+        <v>-5.949253428016553</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-9.508541916920379</v>
       </c>
       <c r="E47">
-        <v>-15.95222651135358</v>
+        <v>-19.43184706868538</v>
       </c>
       <c r="F47">
-        <v>-1.512681861499685</v>
+        <v>-3.015361039363058</v>
       </c>
       <c r="G47">
-        <v>-3.561827028006822</v>
+        <v>-5.717144459167171</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-9.49670654570938</v>
       </c>
       <c r="E48">
-        <v>-14.16543105062109</v>
+        <v>-19.11150734585679</v>
       </c>
       <c r="F48">
-        <v>-1.520224975069577</v>
+        <v>-2.783035460839103</v>
       </c>
       <c r="G48">
-        <v>-4.12155089396802</v>
+        <v>-6.048182460366593</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-9.474656394619458</v>
       </c>
       <c r="E49">
-        <v>-14.05595519148566</v>
+        <v>-18.42922480949114</v>
       </c>
       <c r="F49">
-        <v>-1.510379000119902</v>
+        <v>-2.929191777021645</v>
       </c>
       <c r="G49">
-        <v>-3.722050811016469</v>
+        <v>-5.767285981904973</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-9.452242279269599</v>
       </c>
       <c r="E50">
-        <v>-13.03550433012322</v>
+        <v>-18.10775296816062</v>
       </c>
       <c r="F50">
-        <v>-1.874300680987392</v>
+        <v>-2.88912281738083</v>
       </c>
       <c r="G50">
-        <v>-3.990122236058953</v>
+        <v>-5.314774133233072</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-9.437755661101518</v>
       </c>
       <c r="E51">
-        <v>-13.13949620723536</v>
+        <v>-17.79986654885312</v>
       </c>
       <c r="F51">
-        <v>-1.571202705037859</v>
+        <v>-2.792779546598234</v>
       </c>
       <c r="G51">
-        <v>-4.246745794626638</v>
+        <v>-5.920726457104653</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-9.438821390428986</v>
       </c>
       <c r="E52">
-        <v>-13.85765784316379</v>
+        <v>-16.65989114453222</v>
       </c>
       <c r="F52">
-        <v>-1.828106772770278</v>
+        <v>-3.112009977717288</v>
       </c>
       <c r="G52">
-        <v>-3.807827045938985</v>
+        <v>-5.951686678987917</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-9.454056792973144</v>
       </c>
       <c r="E53">
-        <v>-11.9080909126996</v>
+        <v>-16.79255279058693</v>
       </c>
       <c r="F53">
-        <v>-1.840679733209969</v>
+        <v>-3.22713565099096</v>
       </c>
       <c r="G53">
-        <v>-3.382253106320135</v>
+        <v>-6.438707654361179</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-9.480322915232753</v>
       </c>
       <c r="E54">
-        <v>-11.52385895009678</v>
+        <v>-15.69157660442009</v>
       </c>
       <c r="F54">
-        <v>-2.119253892199623</v>
+        <v>-3.345315514878755</v>
       </c>
       <c r="G54">
-        <v>-3.907994222320713</v>
+        <v>-6.199143336957359</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-9.514222467454053</v>
       </c>
       <c r="E55">
-        <v>-9.951695043431842</v>
+        <v>-15.35407396510242</v>
       </c>
       <c r="F55">
-        <v>-1.444825317331961</v>
+        <v>-2.877993701324219</v>
       </c>
       <c r="G55">
-        <v>-4.955513731311363</v>
+        <v>-6.124712341597926</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-9.54609112030662</v>
       </c>
       <c r="E56">
-        <v>-10.35150948509505</v>
+        <v>-15.46687825263349</v>
       </c>
       <c r="F56">
-        <v>-1.843938530572582</v>
+        <v>-2.695675834539867</v>
       </c>
       <c r="G56">
-        <v>-5.491431464299661</v>
+        <v>-6.245242683591711</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-9.567409378107151</v>
       </c>
       <c r="E57">
-        <v>-10.34523302012042</v>
+        <v>-14.82570973178348</v>
       </c>
       <c r="F57">
-        <v>-2.084331579232401</v>
+        <v>-3.115402970599154</v>
       </c>
       <c r="G57">
-        <v>-5.195534903999603</v>
+        <v>-6.354288743109764</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-9.569621920720044</v>
       </c>
       <c r="E58">
-        <v>-10.02597107410565</v>
+        <v>-15.28497398021938</v>
       </c>
       <c r="F58">
-        <v>-1.445962665776004</v>
+        <v>-2.856409760276875</v>
       </c>
       <c r="G58">
-        <v>-5.207260856299701</v>
+        <v>-6.449933714284849</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-9.542925182826904</v>
       </c>
       <c r="E59">
-        <v>-9.493354603693502</v>
+        <v>-14.93688829714579</v>
       </c>
       <c r="F59">
-        <v>-1.478375025512743</v>
+        <v>-3.168497179281589</v>
       </c>
       <c r="G59">
-        <v>-5.422800544725031</v>
+        <v>-6.43339091822511</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-9.482294035360216</v>
       </c>
       <c r="E60">
-        <v>-7.743683572875898</v>
+        <v>-14.64371036141521</v>
       </c>
       <c r="F60">
-        <v>-1.736616906600684</v>
+        <v>-2.946016747339906</v>
       </c>
       <c r="G60">
-        <v>-5.374168630753137</v>
+        <v>-6.575396769132148</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-9.384925770096034</v>
       </c>
       <c r="E61">
-        <v>-8.579472321153562</v>
+        <v>-14.18915119747327</v>
       </c>
       <c r="F61">
-        <v>-2.060770325194575</v>
+        <v>-2.85914254433871</v>
       </c>
       <c r="G61">
-        <v>-5.203748367482535</v>
+        <v>-6.33800085905655</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-9.251562760364269</v>
       </c>
       <c r="E62">
-        <v>-8.265024143008947</v>
+        <v>-13.9788715069271</v>
       </c>
       <c r="F62">
-        <v>-1.877943012457502</v>
+        <v>-2.960556251993843</v>
       </c>
       <c r="G62">
-        <v>-5.1506703908514</v>
+        <v>-6.926003405014202</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-9.090709261231657</v>
       </c>
       <c r="E63">
-        <v>-9.128246386825079</v>
+        <v>-12.86342684630575</v>
       </c>
       <c r="F63">
-        <v>-1.770562574400005</v>
+        <v>-3.079422004091155</v>
       </c>
       <c r="G63">
-        <v>-5.579283411275301</v>
+        <v>-7.398222931281383</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.90813530367698</v>
       </c>
       <c r="E64">
-        <v>-7.994438764102629</v>
+        <v>-12.85619940178951</v>
       </c>
       <c r="F64">
-        <v>-2.015607734393946</v>
+        <v>-2.739660486893715</v>
       </c>
       <c r="G64">
-        <v>-5.493520418534942</v>
+        <v>-7.431705788865572</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-8.711703954563767</v>
       </c>
       <c r="E65">
-        <v>-7.730510241987584</v>
+        <v>-13.38660597688592</v>
       </c>
       <c r="F65">
-        <v>-1.9722153647331</v>
+        <v>-3.061049643464465</v>
       </c>
       <c r="G65">
-        <v>-5.749306409081191</v>
+        <v>-7.635360618804918</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-8.51210612520725</v>
       </c>
       <c r="E66">
-        <v>-6.352069924896774</v>
+        <v>-11.44659412657791</v>
       </c>
       <c r="F66">
-        <v>-2.134884356723047</v>
+        <v>-3.080571778046241</v>
       </c>
       <c r="G66">
-        <v>-5.540394432825482</v>
+        <v>-7.464086234785184</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-8.315340373044426</v>
       </c>
       <c r="E67">
-        <v>-6.316217996178048</v>
+        <v>-12.30925483961709</v>
       </c>
       <c r="F67">
-        <v>-1.749483937468368</v>
+        <v>-2.811347401931985</v>
       </c>
       <c r="G67">
-        <v>-5.949965195307496</v>
+        <v>-7.412984653840994</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-8.127932354276965</v>
       </c>
       <c r="E68">
-        <v>-7.180246308367544</v>
+        <v>-12.66784205391447</v>
       </c>
       <c r="F68">
-        <v>-1.916220213406061</v>
+        <v>-2.970721976760998</v>
       </c>
       <c r="G68">
-        <v>-5.547422721005355</v>
+        <v>-7.02844492618141</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-7.955802590886417</v>
       </c>
       <c r="E69">
-        <v>-6.028687067535026</v>
+        <v>-11.7279663305705</v>
       </c>
       <c r="F69">
-        <v>-1.637762025852799</v>
+        <v>-2.988492114285853</v>
       </c>
       <c r="G69">
-        <v>-6.106103765121683</v>
+        <v>-7.277606515103577</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-7.800457504484626</v>
       </c>
       <c r="E70">
-        <v>-6.4721107138921</v>
+        <v>-12.95765533345735</v>
       </c>
       <c r="F70">
-        <v>-1.777191170357206</v>
+        <v>-3.008217198881315</v>
       </c>
       <c r="G70">
-        <v>-6.909602962412652</v>
+        <v>-7.337097018444281</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-7.664396304539229</v>
       </c>
       <c r="E71">
-        <v>-7.168907009452337</v>
+        <v>-11.66905088373071</v>
       </c>
       <c r="F71">
-        <v>-2.584368106625698</v>
+        <v>-3.117347148893525</v>
       </c>
       <c r="G71">
-        <v>-5.488819443869176</v>
+        <v>-7.527350760040656</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-7.546690121755507</v>
       </c>
       <c r="E72">
-        <v>-7.164623073041081</v>
+        <v>-12.52554834364545</v>
       </c>
       <c r="F72">
-        <v>-2.05193330174151</v>
+        <v>-3.297506290226181</v>
       </c>
       <c r="G72">
-        <v>-6.093146289880974</v>
+        <v>-7.487544760476459</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-7.444207213849824</v>
       </c>
       <c r="E73">
-        <v>-7.245746156414488</v>
+        <v>-12.30877482137228</v>
       </c>
       <c r="F73">
-        <v>-2.436536003187292</v>
+        <v>-3.559927284861245</v>
       </c>
       <c r="G73">
-        <v>-6.107941117895978</v>
+        <v>-7.829911448511268</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-7.35804540397842</v>
       </c>
       <c r="E74">
-        <v>-7.251615058728429</v>
+        <v>-12.55589364797085</v>
       </c>
       <c r="F74">
-        <v>-2.336500698890418</v>
+        <v>-3.365053024985258</v>
       </c>
       <c r="G74">
-        <v>-6.215182930095128</v>
+        <v>-7.325834542519679</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-7.283429779343408</v>
       </c>
       <c r="E75">
-        <v>-7.777456932025103</v>
+        <v>-13.09291179511845</v>
       </c>
       <c r="F75">
-        <v>-2.555381046099535</v>
+        <v>-3.443380961491771</v>
       </c>
       <c r="G75">
-        <v>-4.843789440452039</v>
+        <v>-6.678169344853282</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-7.216290716875358</v>
       </c>
       <c r="E76">
-        <v>-7.561720430299688</v>
+        <v>-14.24971048037785</v>
       </c>
       <c r="F76">
-        <v>-2.471933799043721</v>
+        <v>-3.498872465437907</v>
       </c>
       <c r="G76">
-        <v>-4.524580018464433</v>
+        <v>-7.079248558027065</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-7.154473025123962</v>
       </c>
       <c r="E77">
-        <v>-7.547206671105104</v>
+        <v>-13.44101106361407</v>
       </c>
       <c r="F77">
-        <v>-2.730626311998784</v>
+        <v>-3.61063993726063</v>
       </c>
       <c r="G77">
-        <v>-5.226660653159831</v>
+        <v>-7.023545318783288</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-7.09236532640344</v>
       </c>
       <c r="E78">
-        <v>-9.263548133226253</v>
+        <v>-13.26586780289341</v>
       </c>
       <c r="F78">
-        <v>-3.039065600961569</v>
+        <v>-3.873538071519707</v>
       </c>
       <c r="G78">
-        <v>-4.852767639954543</v>
+        <v>-6.586361295958214</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-7.025825646837692</v>
       </c>
       <c r="E79">
-        <v>-10.20066601589955</v>
+        <v>-14.36993240833348</v>
       </c>
       <c r="F79">
-        <v>-3.265435217859395</v>
+        <v>-3.900571841710069</v>
       </c>
       <c r="G79">
-        <v>-4.556440708734379</v>
+        <v>-6.790267727358544</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-6.951172241442357</v>
       </c>
       <c r="E80">
-        <v>-9.123622814863248</v>
+        <v>-14.75429569668252</v>
       </c>
       <c r="F80">
-        <v>-3.564966243772474</v>
+        <v>-3.904074179089105</v>
       </c>
       <c r="G80">
-        <v>-4.78586813569695</v>
+        <v>-6.250622320093027</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-6.863495967779502</v>
       </c>
       <c r="E81">
-        <v>-10.92820159302385</v>
+        <v>-15.00366970333691</v>
       </c>
       <c r="F81">
-        <v>-3.0990534831701</v>
+        <v>-4.122650515461394</v>
       </c>
       <c r="G81">
-        <v>-4.647176140874723</v>
+        <v>-6.20790635099981</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-6.761252806155607</v>
       </c>
       <c r="E82">
-        <v>-10.91861934202362</v>
+        <v>-16.71033381650367</v>
       </c>
       <c r="F82">
-        <v>-3.410550276216618</v>
+        <v>-4.061959349327885</v>
       </c>
       <c r="G82">
-        <v>-3.992019178652956</v>
+        <v>-6.520180180082644</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-6.640770531002362</v>
       </c>
       <c r="E83">
-        <v>-12.48000548055031</v>
+        <v>-17.39499380172335</v>
       </c>
       <c r="F83">
-        <v>-3.743931707677696</v>
+        <v>-4.153531223870356</v>
       </c>
       <c r="G83">
-        <v>-4.538931233377173</v>
+        <v>-6.012362357631679</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-6.498177726097493</v>
       </c>
       <c r="E84">
-        <v>-12.41243611988186</v>
+        <v>-17.6953538972301</v>
       </c>
       <c r="F84">
-        <v>-3.64001053189429</v>
+        <v>-4.35739989700594</v>
       </c>
       <c r="G84">
-        <v>-3.997852359893151</v>
+        <v>-6.108815101918346</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-6.335225491915094</v>
       </c>
       <c r="E85">
-        <v>-14.75319527749865</v>
+        <v>-18.56624284754121</v>
       </c>
       <c r="F85">
-        <v>-3.909823877231936</v>
+        <v>-4.516579805495295</v>
       </c>
       <c r="G85">
-        <v>-3.724811805996221</v>
+        <v>-6.250274712811403</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-6.152266571616091</v>
       </c>
       <c r="E86">
-        <v>-16.43931370409261</v>
+        <v>-20.06677535235283</v>
       </c>
       <c r="F86">
-        <v>-3.994697572955371</v>
+        <v>-4.829518786190087</v>
       </c>
       <c r="G86">
-        <v>-3.865735108511917</v>
+        <v>-4.898069145113929</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-5.955658224015338</v>
       </c>
       <c r="E87">
-        <v>-17.60046425287337</v>
+        <v>-21.04903759240859</v>
       </c>
       <c r="F87">
-        <v>-4.53943032030152</v>
+        <v>-4.910359989396694</v>
       </c>
       <c r="G87">
-        <v>-3.398236420183736</v>
+        <v>-6.033943804002188</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-5.757184610694619</v>
       </c>
       <c r="E88">
-        <v>-18.28084483015581</v>
+        <v>-22.02374633781956</v>
       </c>
       <c r="F88">
-        <v>-4.676527610567047</v>
+        <v>-4.905762550311157</v>
       </c>
       <c r="G88">
-        <v>-3.98309725842462</v>
+        <v>-5.74572108826216</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-5.568819861112565</v>
       </c>
       <c r="E89">
-        <v>-18.88151067948122</v>
+        <v>-23.70288185749369</v>
       </c>
       <c r="F89">
-        <v>-4.507549772437378</v>
+        <v>-5.243695860650618</v>
       </c>
       <c r="G89">
-        <v>-3.135432073094232</v>
+        <v>-5.572635835832444</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-5.406355776311002</v>
       </c>
       <c r="E90">
-        <v>-22.18113798043015</v>
+        <v>-24.52891174428482</v>
       </c>
       <c r="F90">
-        <v>-4.453943632700014</v>
+        <v>-5.17710754697658</v>
       </c>
       <c r="G90">
-        <v>-4.482231519926076</v>
+        <v>-5.990800774534406</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-5.284484752391718</v>
       </c>
       <c r="E91">
-        <v>-23.75479628351762</v>
+        <v>-27.00500887609485</v>
       </c>
       <c r="F91">
-        <v>-4.633424341129778</v>
+        <v>-5.408318971343769</v>
       </c>
       <c r="G91">
-        <v>-3.595336369955325</v>
+        <v>-6.021678232779188</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-5.216254363524475</v>
       </c>
       <c r="E92">
-        <v>-25.15101086108854</v>
+        <v>-28.38394732532651</v>
       </c>
       <c r="F92">
-        <v>-5.250673199284398</v>
+        <v>-5.540786516195049</v>
       </c>
       <c r="G92">
-        <v>-4.284277449405355</v>
+        <v>-5.942705168939874</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-5.214021351608974</v>
       </c>
       <c r="E93">
-        <v>-26.91318500864132</v>
+        <v>-29.3338173908054</v>
       </c>
       <c r="F93">
-        <v>-5.297649914697158</v>
+        <v>-5.632468563602093</v>
       </c>
       <c r="G93">
-        <v>-4.855147922197279</v>
+        <v>-6.038280618658633</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-5.280837442039667</v>
       </c>
       <c r="E94">
-        <v>-30.06745508665504</v>
+        <v>-33.14308594928856</v>
       </c>
       <c r="F94">
-        <v>-4.907328993069851</v>
+        <v>-5.905174567910316</v>
       </c>
       <c r="G94">
-        <v>-4.990357223112192</v>
+        <v>-6.604354110964153</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-5.415545505998451</v>
       </c>
       <c r="E95">
-        <v>-30.8470930214746</v>
+        <v>-34.53359238537281</v>
       </c>
       <c r="F95">
-        <v>-5.199402227255526</v>
+        <v>-6.329240692425467</v>
       </c>
       <c r="G95">
-        <v>-4.902597971411653</v>
+        <v>-6.773698446934492</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.613662726799026</v>
       </c>
       <c r="E96">
-        <v>-33.88823049759169</v>
+        <v>-36.15085536468014</v>
       </c>
       <c r="F96">
-        <v>-5.596159563602585</v>
+        <v>-6.243814061460663</v>
       </c>
       <c r="G96">
-        <v>-4.168408355530864</v>
+        <v>-7.394088059902834</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.856508261104906</v>
       </c>
       <c r="E97">
-        <v>-36.09407282909796</v>
+        <v>-38.52987107071373</v>
       </c>
       <c r="F97">
-        <v>-5.911053491367984</v>
+        <v>-6.426259911008747</v>
       </c>
       <c r="G97">
-        <v>-5.767991128104837</v>
+        <v>-7.347147834701508</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-6.133523789906733</v>
       </c>
       <c r="E98">
-        <v>-39.21836440918091</v>
+        <v>-41.19566824294208</v>
       </c>
       <c r="F98">
-        <v>-5.668825608910963</v>
+        <v>-6.772832264992005</v>
       </c>
       <c r="G98">
-        <v>-6.443074263927478</v>
+        <v>-7.480261560290063</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-6.414621944447989</v>
       </c>
       <c r="E99">
-        <v>-40.53122562992964</v>
+        <v>-43.5006049069212</v>
       </c>
       <c r="F99">
-        <v>-6.465101230158613</v>
+        <v>-6.629009459783148</v>
       </c>
       <c r="G99">
-        <v>-6.487753386525482</v>
+        <v>-8.346124814449825</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-6.697196842262213</v>
       </c>
       <c r="E100">
-        <v>-44.30992472462403</v>
+        <v>-46.70840834041659</v>
       </c>
       <c r="F100">
-        <v>-6.368666424778008</v>
+        <v>-6.895230175694854</v>
       </c>
       <c r="G100">
-        <v>-6.944982762590844</v>
+        <v>-8.208541852383252</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-6.942545195010486</v>
       </c>
       <c r="E101">
-        <v>-46.55407568199818</v>
+        <v>-48.48188782332952</v>
       </c>
       <c r="F101">
-        <v>-6.642509363346572</v>
+        <v>-6.927713775028233</v>
       </c>
       <c r="G101">
-        <v>-7.473607363756128</v>
+        <v>-8.642408708577978</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-7.183584305786662</v>
       </c>
       <c r="E102">
-        <v>-50.07298414770203</v>
+        <v>-50.47890410444608</v>
       </c>
       <c r="F102">
-        <v>-6.534494810042232</v>
+        <v>-7.049683005600134</v>
       </c>
       <c r="G102">
-        <v>-8.168096917529976</v>
+        <v>-9.835737885300288</v>
       </c>
     </row>
   </sheetData>
